--- a/docs/rocket_parts.xlsx
+++ b/docs/rocket_parts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mainport365-my.sharepoint.com/personal/bzelissen_mainport_nl/Documents/Documenten/Arduino/sketches/ESP-Controlled-Rocket/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="704" documentId="11_F25DC773A252ABDACC10484BC95F46505ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6859EA7-D7AB-4A10-B36B-46D5DAD37B45}"/>
+  <xr:revisionPtr revIDLastSave="1110" documentId="11_F25DC773A252ABDACC10484BC95F46505ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C44916A8-87DA-4244-BF40-A6D6082FB45D}"/>
   <bookViews>
-    <workbookView xWindow="11940" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="1" r:id="rId1"/>
@@ -42,41 +42,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="148">
   <si>
     <t>Part</t>
   </si>
   <si>
-    <t># Parts 1.5L Rocket</t>
-  </si>
-  <si>
-    <t>Total weight 1.5L Rocket</t>
-  </si>
-  <si>
-    <t># Parts 4.5L Rocket</t>
-  </si>
-  <si>
-    <t>Total weight 4.5L Rocket</t>
-  </si>
-  <si>
-    <t># Parts 7.5L Rocket</t>
-  </si>
-  <si>
-    <t>Total weight 7.5L Rocket</t>
-  </si>
-  <si>
-    <t># Parts 10.5L Rocket</t>
-  </si>
-  <si>
-    <t>Total weight 10.5L Rocket</t>
-  </si>
-  <si>
-    <t>Nozzle</t>
-  </si>
-  <si>
-    <t>Nozzle Connector</t>
-  </si>
-  <si>
     <t>Bottle Connector</t>
   </si>
   <si>
@@ -95,18 +65,6 @@
     <t>Battery</t>
   </si>
   <si>
-    <t>Parachute Small</t>
-  </si>
-  <si>
-    <t>Parachute Medium</t>
-  </si>
-  <si>
-    <t>Parachute Large</t>
-  </si>
-  <si>
-    <t>Nose Cone Adapter Ring</t>
-  </si>
-  <si>
     <t>Nose Cone Ejection Hatch</t>
   </si>
   <si>
@@ -120,12 +78,6 @@
   </si>
   <si>
     <t>Battery Mount</t>
-  </si>
-  <si>
-    <t># Parts 13.5L Rocket</t>
-  </si>
-  <si>
-    <t>Total weight 13.5L Rocket</t>
   </si>
   <si>
     <t>Fins Type 1</t>
@@ -461,13 +413,88 @@
   </si>
   <si>
     <t>Parachute Mechanical Trigger Part Stick</t>
+  </si>
+  <si>
+    <t>Nose Cone Ejection Hatch + Adapter Ring</t>
+  </si>
+  <si>
+    <t>Nose Cone Tip C</t>
+  </si>
+  <si>
+    <t>Nozzle A</t>
+  </si>
+  <si>
+    <t>Parachute Small 65cm</t>
+  </si>
+  <si>
+    <t>Parachute Medium 90cm</t>
+  </si>
+  <si>
+    <t>Parachute Large 150cm</t>
+  </si>
+  <si>
+    <t>Payload Bottle Connector Type C</t>
+  </si>
+  <si>
+    <t>Payload Bottle Connector Type D</t>
+  </si>
+  <si>
+    <t>Payload Body A/B/C</t>
+  </si>
+  <si>
+    <t>Flight Computer Mount A/B/C</t>
+  </si>
+  <si>
+    <t>Battery Mount A/B/C</t>
+  </si>
+  <si>
+    <t>Nose Cone Tip A</t>
+  </si>
+  <si>
+    <t>Nose Cone Ejection Hatch A/B/C</t>
+  </si>
+  <si>
+    <t>Nose Cone Adapter Ring A/B/C</t>
+  </si>
+  <si>
+    <t>Nozzle Connector A/B/C</t>
+  </si>
+  <si>
+    <t>Payload Body D</t>
+  </si>
+  <si>
+    <t>Parachute Body Type A</t>
+  </si>
+  <si>
+    <t>Parachute + Nose Cone Body Type B</t>
+  </si>
+  <si>
+    <t>Parachute + Nose Cone Body Type C</t>
+  </si>
+  <si>
+    <t>Parachute Body Type D</t>
+  </si>
+  <si>
+    <t>Nose Cone Tip D</t>
+  </si>
+  <si>
+    <t>Flight Computer Mount D</t>
+  </si>
+  <si>
+    <t>Nozzle + Connector D</t>
+  </si>
+  <si>
+    <t>Nozzle + Connector E</t>
+  </si>
+  <si>
+    <t>Payload Bottle Connector + Body + Payload +FC + Bat + Para + EH Type E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +518,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -500,7 +534,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -580,11 +614,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -592,9 +658,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -609,12 +672,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Procent" xfId="1" builtinId="5"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -947,1160 +1025,2531 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="13.7109375" style="8" customWidth="1"/>
-    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="10" width="14.85546875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" customWidth="1"/>
+    <col min="13" max="18" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="15" t="str">
+        <f>_xlfn.CONCAT("# Parts ",C39," L Rocket A")</f>
+        <v># Parts 1,5 L Rocket A</v>
+      </c>
+      <c r="D1" s="16" t="str">
+        <f>_xlfn.CONCAT("Total Weight ",C39," L Rocket A")</f>
+        <v>Total Weight 1,5 L Rocket A</v>
+      </c>
+      <c r="E1" s="15" t="str">
+        <f>_xlfn.CONCAT("# Parts ",E39," L Rocket B")</f>
+        <v># Parts 4,125 L Rocket B</v>
+      </c>
+      <c r="F1" s="16" t="str">
+        <f>_xlfn.CONCAT("Total Weight ",E39," L Rocket B")</f>
+        <v>Total Weight 4,125 L Rocket B</v>
+      </c>
+      <c r="G1" s="15" t="str">
+        <f>_xlfn.CONCAT("# Parts ",G39," L Rocket B")</f>
+        <v># Parts 6,75 L Rocket B</v>
+      </c>
+      <c r="H1" s="16" t="str">
+        <f>_xlfn.CONCAT("Total Weight ",G39," L Rocket B")</f>
+        <v>Total Weight 6,75 L Rocket B</v>
+      </c>
+      <c r="I1" s="15" t="str">
+        <f>_xlfn.CONCAT("# Parts ",I39," L Rocket B")</f>
+        <v># Parts 9,375 L Rocket B</v>
+      </c>
+      <c r="J1" s="16" t="str">
+        <f>_xlfn.CONCAT("Total Weight ",I39," L Rocket B")</f>
+        <v>Total Weight 9,375 L Rocket B</v>
+      </c>
+      <c r="K1" s="15" t="str">
+        <f>_xlfn.CONCAT("# Parts ",K39," L Rocket B")</f>
+        <v># Parts 12 L Rocket B</v>
+      </c>
+      <c r="L1" s="16" t="str">
+        <f>_xlfn.CONCAT("Total Weight ",K39," L Rocket B")</f>
+        <v>Total Weight 12 L Rocket B</v>
+      </c>
+      <c r="M1" s="15" t="str">
+        <f>_xlfn.CONCAT("# Parts ",M39," L Rocket C")</f>
+        <v># Parts 12 L Rocket C</v>
+      </c>
+      <c r="N1" s="16" t="str">
+        <f>_xlfn.CONCAT("Total Weight ",M39," L Rocket C")</f>
+        <v>Total Weight 12 L Rocket C</v>
+      </c>
+      <c r="O1" s="15" t="str">
+        <f>_xlfn.CONCAT("# Parts ",O39," L Rocket D")</f>
+        <v># Parts 12 L Rocket D</v>
+      </c>
+      <c r="P1" s="16" t="str">
+        <f>_xlfn.CONCAT("Total Weight ",O39," L Rocket D")</f>
+        <v>Total Weight 12 L Rocket D</v>
+      </c>
+      <c r="Q1" s="15" t="str">
+        <f>_xlfn.CONCAT("# Parts ",Q39," L Rocket E")</f>
+        <v># Parts 12 L Rocket E</v>
+      </c>
+      <c r="R1" s="16" t="str">
+        <f>_xlfn.CONCAT("Total Weight ",Q39," L Rocket E")</f>
+        <v>Total Weight 12 L Rocket E</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2">
         <v>19</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
       <c r="D2" s="8">
         <f>B2*C2</f>
         <v>19</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>1</v>
       </c>
       <c r="F2" s="8">
         <f>B2*E2</f>
         <v>19</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="11">
         <v>1</v>
       </c>
       <c r="H2" s="8">
         <f>B2*G2</f>
         <v>19</v>
       </c>
-      <c r="I2" s="8">
-        <v>1</v>
-      </c>
-      <c r="J2" s="9">
+      <c r="I2" s="11">
+        <v>1</v>
+      </c>
+      <c r="J2" s="8">
         <f>B2*I2</f>
         <v>19</v>
       </c>
-      <c r="K2" s="8">
-        <v>1</v>
-      </c>
-      <c r="L2" s="9">
-        <f t="shared" ref="L2:L26" si="0">B2*K2</f>
+      <c r="K2" s="7">
+        <v>1</v>
+      </c>
+      <c r="L2" s="8">
+        <f>B2*K2</f>
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="7">
+        <v>1</v>
+      </c>
+      <c r="N2" s="8">
+        <f>B2*M2</f>
+        <v>19</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="8">
+        <f>B2*O2</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <f>$B2*Q2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="B3" s="2">
         <v>23</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>1</v>
       </c>
       <c r="D3" s="8">
-        <f t="shared" ref="D3:D26" si="1">B3*C3</f>
+        <f t="shared" ref="D3:D35" si="0">B3*C3</f>
         <v>23</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>1</v>
       </c>
       <c r="F3" s="8">
-        <f t="shared" ref="F3:F26" si="2">B3*E3</f>
+        <f t="shared" ref="F3:F38" si="1">B3*E3</f>
         <v>23</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="11">
         <v>1</v>
       </c>
       <c r="H3" s="8">
-        <f t="shared" ref="H3:H26" si="3">B3*G3</f>
+        <f t="shared" ref="H3:H34" si="2">B3*G3</f>
         <v>23</v>
       </c>
-      <c r="I3" s="8">
-        <v>1</v>
-      </c>
-      <c r="J3" s="9">
-        <f t="shared" ref="J3:J26" si="4">B3*I3</f>
+      <c r="I3" s="11">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8">
+        <f t="shared" ref="J3:J36" si="3">B3*I3</f>
         <v>23</v>
       </c>
-      <c r="K3" s="8">
-        <v>1</v>
-      </c>
-      <c r="L3" s="9">
+      <c r="K3" s="7">
+        <v>1</v>
+      </c>
+      <c r="L3" s="8">
+        <f>B3*K3</f>
+        <v>23</v>
+      </c>
+      <c r="M3" s="7">
+        <v>1</v>
+      </c>
+      <c r="N3" s="8">
+        <f>B3*M3</f>
+        <v>23</v>
+      </c>
+      <c r="O3" s="7">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <f>B3*O3</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
+        <f t="shared" ref="R3:R38" si="4">$B3*Q3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="2">
+        <v>12</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8">
+        <f>B4*K4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="7">
+        <v>0</v>
+      </c>
+      <c r="N4" s="8">
+        <f>B4*M4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="7">
+        <v>1</v>
+      </c>
+      <c r="P4" s="8">
+        <f>B4*O4</f>
+        <v>12</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="2">
+        <v>14</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8">
+        <f t="shared" ref="D5" si="5">B5*C5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" ref="F5" si="6">B5*E5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" ref="H5" si="7">B5*G5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" ref="J5" si="8">B5*I5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <f>B5*K5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8">
+        <f>B5*M5</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <f>B5*O5</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>1</v>
+      </c>
+      <c r="R5" s="8">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2">
         <v>26</v>
       </c>
-      <c r="C4" s="8">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="C6" s="11">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="8">
-        <v>1</v>
-      </c>
-      <c r="F4" s="8">
+        <v>26</v>
+      </c>
+      <c r="G6" s="11">
+        <v>2</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="I6" s="11">
+        <v>3</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" si="3"/>
+        <v>78</v>
+      </c>
+      <c r="K6" s="7">
+        <v>4</v>
+      </c>
+      <c r="L6" s="8">
+        <f>B6*K6</f>
+        <v>104</v>
+      </c>
+      <c r="M6" s="7">
+        <v>4</v>
+      </c>
+      <c r="N6" s="8">
+        <f>B6*M6</f>
+        <v>104</v>
+      </c>
+      <c r="O6" s="7">
+        <v>4</v>
+      </c>
+      <c r="P6" s="8">
+        <f>B6*O6</f>
+        <v>104</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>4</v>
+      </c>
+      <c r="R6" s="8">
+        <f t="shared" si="4"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2">
+        <v>41</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="G7" s="11">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="K7" s="7">
+        <v>1</v>
+      </c>
+      <c r="L7" s="8">
+        <f>B7*K7</f>
+        <v>41</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8">
+        <f>B7*M7</f>
+        <v>41</v>
+      </c>
+      <c r="O7" s="7">
+        <v>1</v>
+      </c>
+      <c r="P7" s="8">
+        <f>B7*O7</f>
+        <v>41</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>1</v>
+      </c>
+      <c r="R7" s="8">
+        <f t="shared" si="4"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2">
+        <v>80</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="G8" s="11">
+        <v>2</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+      <c r="I8" s="11">
+        <v>3</v>
+      </c>
+      <c r="J8" s="8">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="K8" s="7">
+        <v>4</v>
+      </c>
+      <c r="L8" s="8">
+        <f>B8*K8</f>
+        <v>320</v>
+      </c>
+      <c r="M8" s="7">
+        <v>4</v>
+      </c>
+      <c r="N8" s="8">
+        <f>B8*M8</f>
+        <v>320</v>
+      </c>
+      <c r="O8" s="7">
+        <v>4</v>
+      </c>
+      <c r="P8" s="8">
+        <f>B8*O8</f>
+        <v>320</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>4</v>
+      </c>
+      <c r="R8" s="8">
+        <f t="shared" si="4"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="2">
+        <v>43</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="7">
+        <v>1</v>
+      </c>
+      <c r="L9" s="8">
+        <f>B9*K9</f>
+        <v>43</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8">
+        <f>B9*M9</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8">
+        <f>B9*O9</f>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="2">
+        <v>47</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="G10" s="11">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="I10" s="11">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8">
+        <f>B10*K10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8">
+        <f>B10*M10</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <f>B10*O10</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="2">
+        <v>40</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <f>B11*K11</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
+        <v>1</v>
+      </c>
+      <c r="N11" s="8">
+        <f>B11*M11</f>
+        <v>40</v>
+      </c>
+      <c r="O11" s="7">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <f>B11*O11</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="2">
+        <v>26</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="7">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
+        <f>B12*K12</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="7">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8">
+        <f>B12*M12</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="7">
+        <v>1</v>
+      </c>
+      <c r="P12" s="8">
+        <f>B12*O12</f>
+        <v>26</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="2">
+        <v>400</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="11">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="7">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <f>B13*K13</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <f>B13*M13</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="7">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8">
+        <f>B13*O13</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>1</v>
+      </c>
+      <c r="R13" s="8">
+        <f t="shared" si="4"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="2">
+        <v>74</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="11">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="G14" s="11">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="I14" s="11">
+        <v>1</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="3"/>
+        <v>74</v>
+      </c>
+      <c r="K14" s="7">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8">
+        <f>B14*K14</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="7">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
+        <f>B14*M14</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="7">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <f>B14*O14</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="2">
+        <v>40</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="7">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <f>B15*K15</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="7">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <f>B15*M15</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="7">
+        <v>1</v>
+      </c>
+      <c r="P15" s="8">
+        <f>B15*O15</f>
+        <v>40</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2">
+        <v>40</v>
+      </c>
+      <c r="C16" s="11">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="11">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="G16" s="11">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="I16" s="11">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="K16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8">
+        <f>B16*K16</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="7">
+        <v>1</v>
+      </c>
+      <c r="N16" s="8">
+        <f>B16*M16</f>
+        <v>40</v>
+      </c>
+      <c r="O16" s="7">
+        <v>1</v>
+      </c>
+      <c r="P16" s="8">
+        <f>B16*O16</f>
+        <v>40</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="2">
+        <v>7</v>
+      </c>
+      <c r="C17" s="11">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="11">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8">
+        <f>B17*E17</f>
+        <v>7</v>
+      </c>
+      <c r="G17" s="11">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="I17" s="11">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8">
+        <f>B17*I17</f>
+        <v>7</v>
+      </c>
+      <c r="K17" s="7">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <f>B17*K17</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <f>B17*M17</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="7">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8">
+        <f>B17*O17</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" ref="F18:F23" si="9">B18*E18</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" ref="J18:J23" si="10">B18*I18</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <f>B18*K18</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8">
+        <f>B18*M18</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="7">
+        <v>1</v>
+      </c>
+      <c r="P18" s="8">
+        <f>B18*O18</f>
+        <v>4</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2">
+        <v>97</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8">
+        <f t="shared" si="9"/>
+        <v>97</v>
+      </c>
+      <c r="G19" s="11">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+      <c r="I19" s="11">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8">
+        <f t="shared" si="10"/>
+        <v>97</v>
+      </c>
+      <c r="K19" s="7">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <f>B19*K19</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="7">
+        <v>1</v>
+      </c>
+      <c r="N19" s="8">
+        <f>B19*M19</f>
+        <v>97</v>
+      </c>
+      <c r="O19" s="7">
+        <v>1</v>
+      </c>
+      <c r="P19" s="8">
+        <f>B19*O19</f>
+        <v>97</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="2">
+        <v>8</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="11">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="G20" s="11">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="I20" s="11">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="K20" s="7">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8">
+        <f>B20*K20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="7">
+        <v>0</v>
+      </c>
+      <c r="N20" s="8">
+        <f>B20*M20</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="7">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8">
+        <f>B20*O20</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="2">
+        <v>26</v>
+      </c>
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="7">
+        <v>1</v>
+      </c>
+      <c r="L21" s="8">
+        <f>B21*K21</f>
+        <v>26</v>
+      </c>
+      <c r="M21" s="7">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <f>B21*M21</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="7">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8">
+        <f>B21*O21</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="2">
+        <v>66</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0</v>
+      </c>
+      <c r="D22" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="11">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8">
+        <f t="shared" si="9"/>
+        <v>66</v>
+      </c>
+      <c r="G22" s="11">
+        <v>1</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="I22" s="11">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="10"/>
+        <v>66</v>
+      </c>
+      <c r="K22" s="7">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8">
+        <f>B22*K22</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="7">
+        <v>1</v>
+      </c>
+      <c r="N22" s="8">
+        <f>B22*M22</f>
+        <v>66</v>
+      </c>
+      <c r="O22" s="7">
+        <v>1</v>
+      </c>
+      <c r="P22" s="8">
+        <f>B22*O22</f>
+        <v>66</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="2">
+        <v>100</v>
+      </c>
+      <c r="C23" s="11">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="11">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="11">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="7">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
+        <f>B23*K23</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="7">
+        <v>0</v>
+      </c>
+      <c r="N23" s="8">
+        <f>B23*M23</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="7">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8">
+        <f>B23*O23</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="2">
+        <v>42</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="11">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="G24" s="11">
+        <v>1</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="I24" s="11">
+        <v>1</v>
+      </c>
+      <c r="J24" s="8">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="K24" s="7">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8">
+        <f>B24*K24</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="7">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8">
+        <f>B24*M24</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="7">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8">
+        <f>B24*O24</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>0</v>
+      </c>
+      <c r="R24" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="2">
+        <v>10</v>
+      </c>
+      <c r="C25" s="11">
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="11">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="7">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <f>B25*K25</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="7">
+        <v>1</v>
+      </c>
+      <c r="N25" s="8">
+        <f>B25*M25</f>
+        <v>10</v>
+      </c>
+      <c r="O25" s="7">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8">
+        <f>B25*O25</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>0</v>
+      </c>
+      <c r="R25" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="2">
+        <v>25</v>
+      </c>
+      <c r="C26" s="11">
+        <v>0</v>
+      </c>
+      <c r="D26" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="11">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="7">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8">
+        <f>B26*K26</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="7">
+        <v>0</v>
+      </c>
+      <c r="N26" s="8">
+        <f>B26*M26</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="7">
+        <v>1</v>
+      </c>
+      <c r="P26" s="8">
+        <f>B26*O26</f>
+        <v>25</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>0</v>
+      </c>
+      <c r="R26" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="2">
+        <v>36</v>
+      </c>
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+      <c r="D27" s="8">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="E27" s="11">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="11">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="11">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="7">
+        <v>1</v>
+      </c>
+      <c r="L27" s="8">
+        <f>B27*K27</f>
+        <v>36</v>
+      </c>
+      <c r="M27" s="7">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
+        <f>B27*M27</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="7">
+        <v>0</v>
+      </c>
+      <c r="P27" s="8">
+        <f>B27*O27</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" s="2">
+        <v>30</v>
+      </c>
+      <c r="C28" s="11">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="11">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="11">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="7">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8">
+        <f>B28*K28</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="7">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8">
+        <f>B28*M28</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="7">
+        <v>1</v>
+      </c>
+      <c r="P28" s="8">
+        <f>B28*O28</f>
+        <v>30</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>0</v>
+      </c>
+      <c r="R28" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="2">
+        <v>100</v>
+      </c>
+      <c r="C29" s="11">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="11">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="G29" s="11">
+        <v>1</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="I29" s="11">
+        <v>1</v>
+      </c>
+      <c r="J29" s="8">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="K29" s="7">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <f>B29*K29</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="7">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
+        <f>B29*M29</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="7">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8">
+        <f>B29*O29</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="7">
+        <v>0</v>
+      </c>
+      <c r="R29" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="2">
+        <v>129</v>
+      </c>
+      <c r="C30" s="11">
+        <v>0</v>
+      </c>
+      <c r="D30" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="11">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="11">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="7">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8">
+        <f>B30*K30</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="7">
+        <v>1</v>
+      </c>
+      <c r="N30" s="8">
+        <f>B30*M30</f>
+        <v>129</v>
+      </c>
+      <c r="O30" s="7">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8">
+        <f>B30*O30</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="7">
+        <v>0</v>
+      </c>
+      <c r="R30" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="2">
+        <v>123</v>
+      </c>
+      <c r="C31" s="11">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="11">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="G31" s="11">
+        <v>1</v>
+      </c>
+      <c r="H31" s="8">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="I31" s="11">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8">
+        <f t="shared" si="3"/>
+        <v>123</v>
+      </c>
+      <c r="K31" s="7">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <f>B31*K31</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="7">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8">
+        <f>B31*M31</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="7">
+        <v>0</v>
+      </c>
+      <c r="P31" s="8">
+        <f>B31*O31</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>0</v>
+      </c>
+      <c r="R31" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="2">
+        <v>110</v>
+      </c>
+      <c r="C32" s="11">
+        <v>0</v>
+      </c>
+      <c r="D32" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E32" s="11">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="11">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="11">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="7">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8">
+        <f>B32*K32</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="7">
+        <v>1</v>
+      </c>
+      <c r="N32" s="8">
+        <f>B32*M32</f>
+        <v>110</v>
+      </c>
+      <c r="O32" s="7">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8">
+        <f>B32*O32</f>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="7">
+        <v>0</v>
+      </c>
+      <c r="R32" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="2">
+        <v>26</v>
+      </c>
+      <c r="C33" s="11">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="11">
+        <v>1</v>
+      </c>
+      <c r="F33" s="8">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="G33" s="11">
+        <v>1</v>
+      </c>
+      <c r="H33" s="8">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="G4" s="8">
-        <v>2</v>
-      </c>
-      <c r="H4" s="8">
-        <f t="shared" si="3"/>
-        <v>52</v>
-      </c>
-      <c r="I4" s="8">
-        <v>3</v>
-      </c>
-      <c r="J4" s="9">
-        <f t="shared" si="4"/>
-        <v>78</v>
-      </c>
-      <c r="K4" s="8">
-        <v>4</v>
-      </c>
-      <c r="L4" s="9">
-        <f t="shared" si="0"/>
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2">
-        <v>41.25</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8">
-        <f t="shared" si="1"/>
-        <v>41.25</v>
-      </c>
-      <c r="E5" s="8">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8">
-        <f t="shared" si="2"/>
-        <v>41.25</v>
-      </c>
-      <c r="G5" s="8">
-        <v>1</v>
-      </c>
-      <c r="H5" s="8">
-        <f t="shared" si="3"/>
-        <v>41.25</v>
-      </c>
-      <c r="I5" s="8">
-        <v>1</v>
-      </c>
-      <c r="J5" s="9">
-        <f t="shared" si="4"/>
-        <v>41.25</v>
-      </c>
-      <c r="K5" s="8">
-        <v>1</v>
-      </c>
-      <c r="L5" s="9">
-        <f t="shared" si="0"/>
-        <v>41.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
-        <v>80</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="G6" s="8">
-        <v>2</v>
-      </c>
-      <c r="H6" s="8">
-        <f t="shared" si="3"/>
-        <v>160</v>
-      </c>
-      <c r="I6" s="8">
-        <v>3</v>
-      </c>
-      <c r="J6" s="9">
-        <f t="shared" si="4"/>
-        <v>240</v>
-      </c>
-      <c r="K6" s="8">
-        <v>4</v>
-      </c>
-      <c r="L6" s="9">
-        <f>B6*K6</f>
-        <v>320</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="2">
-        <v>43</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="2">
-        <v>47</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
-        <f t="shared" si="2"/>
-        <v>47</v>
-      </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8">
-        <f t="shared" si="3"/>
-        <v>47</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1</v>
-      </c>
-      <c r="J8" s="9">
-        <f t="shared" si="4"/>
-        <v>47</v>
-      </c>
-      <c r="K8" s="8">
-        <v>1</v>
-      </c>
-      <c r="L8" s="9">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2">
-        <v>74</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
-        <f>B9*C9</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" si="2"/>
-        <v>74</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="3"/>
-        <v>74</v>
-      </c>
-      <c r="I9" s="8">
-        <v>1</v>
-      </c>
-      <c r="J9" s="9">
-        <f t="shared" si="4"/>
-        <v>74</v>
-      </c>
-      <c r="K9" s="8">
-        <v>1</v>
-      </c>
-      <c r="L9" s="9">
-        <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="2">
-        <v>40</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <f t="shared" ref="D10:D16" si="5">B10*C10</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
-        <f t="shared" si="3"/>
-        <v>40</v>
-      </c>
-      <c r="I10" s="8">
-        <v>1</v>
-      </c>
-      <c r="J10" s="9">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="K10" s="8">
-        <v>1</v>
-      </c>
-      <c r="L10" s="9">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2">
-        <v>7</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="G11" s="8">
-        <v>1</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="I11" s="8">
-        <v>1</v>
-      </c>
-      <c r="J11" s="9">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="K11" s="8">
-        <v>1</v>
-      </c>
-      <c r="L11" s="9">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="2">
-        <v>97</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8">
-        <f t="shared" si="2"/>
-        <v>97</v>
-      </c>
-      <c r="G12" s="8">
-        <v>1</v>
-      </c>
-      <c r="H12" s="8">
-        <f t="shared" si="3"/>
-        <v>97</v>
-      </c>
-      <c r="I12" s="8">
-        <v>1</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" si="4"/>
-        <v>97</v>
-      </c>
-      <c r="K12" s="8">
-        <v>1</v>
-      </c>
-      <c r="L12" s="9">
-        <f t="shared" si="0"/>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2">
-        <v>8</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="G13" s="8">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="I13" s="8">
-        <v>1</v>
-      </c>
-      <c r="J13" s="9">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="K13" s="8">
-        <v>1</v>
-      </c>
-      <c r="L13" s="9">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2">
-        <v>26</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1</v>
-      </c>
-      <c r="D14" s="8">
-        <f t="shared" si="5"/>
-        <v>26</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="8">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="8">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="2">
-        <v>66</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8">
-        <f t="shared" ref="F15" si="6">B15*E15</f>
-        <v>66</v>
-      </c>
-      <c r="G15" s="8">
-        <v>1</v>
-      </c>
-      <c r="H15" s="8">
-        <f t="shared" si="3"/>
-        <v>66</v>
-      </c>
-      <c r="I15" s="8">
-        <v>1</v>
-      </c>
-      <c r="J15" s="9">
-        <f t="shared" si="4"/>
-        <v>66</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="2">
-        <v>100</v>
-      </c>
-      <c r="C16" s="8">
-        <v>0</v>
-      </c>
-      <c r="D16" s="8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0</v>
-      </c>
-      <c r="F16" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="8">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="8">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="8">
-        <v>1</v>
-      </c>
-      <c r="L16" s="9">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="2">
-        <v>42</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
-        <f t="shared" ref="D17:D18" si="7">B17*C17</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8">
-        <f t="shared" si="2"/>
-        <v>42</v>
-      </c>
-      <c r="G17" s="8">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8">
-        <f t="shared" si="3"/>
-        <v>42</v>
-      </c>
-      <c r="I17" s="8">
-        <v>1</v>
-      </c>
-      <c r="J17" s="9">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="K17" s="8">
-        <v>1</v>
-      </c>
-      <c r="L17" s="9">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B18" s="2">
-        <v>36</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8">
-        <f t="shared" si="7"/>
-        <v>36</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="8">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="8">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="8">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="2">
-        <v>100</v>
-      </c>
-      <c r="C19" s="8">
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8">
-        <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="G19" s="8">
-        <v>1</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="I19" s="8">
-        <v>1</v>
-      </c>
-      <c r="J19" s="9">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="K19" s="8">
-        <v>1</v>
-      </c>
-      <c r="L19" s="9">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="2">
-        <v>123</v>
-      </c>
-      <c r="C20" s="8">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8">
-        <f t="shared" si="2"/>
-        <v>123</v>
-      </c>
-      <c r="G20" s="8">
-        <v>1</v>
-      </c>
-      <c r="H20" s="8">
-        <f t="shared" si="3"/>
-        <v>123</v>
-      </c>
-      <c r="I20" s="8">
-        <v>1</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" si="4"/>
-        <v>123</v>
-      </c>
-      <c r="K20" s="8">
-        <v>1</v>
-      </c>
-      <c r="L20" s="9">
-        <f t="shared" si="0"/>
-        <v>123</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2">
-        <v>26</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="2"/>
-        <v>26</v>
-      </c>
-      <c r="G21" s="8">
-        <v>1</v>
-      </c>
-      <c r="H21" s="8">
+      <c r="I33" s="11">
+        <v>1</v>
+      </c>
+      <c r="J33" s="8">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="I21" s="8">
-        <v>1</v>
-      </c>
-      <c r="J21" s="9">
+      <c r="K33" s="7">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <f>B33*K33</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="7">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8">
+        <f>B33*M33</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="7">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8">
+        <f>B33*O33</f>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8">
         <f t="shared" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="K21" s="8">
-        <v>1</v>
-      </c>
-      <c r="L21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="2">
+        <v>15</v>
+      </c>
+      <c r="C34" s="11">
+        <v>0</v>
+      </c>
+      <c r="D34" s="8">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="2">
-        <v>15</v>
-      </c>
-      <c r="C22" s="8">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8">
+        <v>0</v>
+      </c>
+      <c r="E34" s="11">
+        <v>3</v>
+      </c>
+      <c r="F34" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
+        <v>45</v>
+      </c>
+      <c r="G34" s="11">
         <v>3</v>
       </c>
-      <c r="F22" s="8">
+      <c r="H34" s="8">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="G22" s="8">
+      <c r="I34" s="11">
         <v>3</v>
       </c>
-      <c r="H22" s="8">
+      <c r="J34" s="8">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="I22" s="8">
-        <v>3</v>
-      </c>
-      <c r="J22" s="9">
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8">
+        <f>B34*K34</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="7">
+        <v>1</v>
+      </c>
+      <c r="N34" s="8">
+        <f>B34*M34</f>
+        <v>15</v>
+      </c>
+      <c r="O34" s="7">
+        <v>1</v>
+      </c>
+      <c r="P34" s="8">
+        <f>B34*O34</f>
+        <v>15</v>
+      </c>
+      <c r="Q34" s="7">
+        <v>1</v>
+      </c>
+      <c r="R34" s="8">
         <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="K22" s="8">
-        <v>3</v>
-      </c>
-      <c r="L22" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="2">
+        <v>5</v>
+      </c>
+      <c r="C35" s="11">
+        <v>0</v>
+      </c>
+      <c r="D35" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="2">
-        <v>5</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11">
+        <v>2</v>
+      </c>
+      <c r="F35" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E23" s="8">
+        <v>10</v>
+      </c>
+      <c r="G35" s="11">
         <v>2</v>
       </c>
-      <c r="F23" s="8">
-        <f t="shared" si="2"/>
+      <c r="H35" s="8">
+        <f t="shared" ref="H35:H38" si="11">B35*G35</f>
         <v>10</v>
       </c>
-      <c r="G23" s="8">
+      <c r="I35" s="11">
         <v>2</v>
       </c>
-      <c r="H23" s="8">
+      <c r="J35" s="8">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="I23" s="8">
-        <v>2</v>
-      </c>
-      <c r="J23" s="9">
+      <c r="K35" s="7">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8">
+        <f>B35*K35</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="7">
+        <v>1</v>
+      </c>
+      <c r="N35" s="8">
+        <f>B35*M35</f>
+        <v>5</v>
+      </c>
+      <c r="O35" s="7">
+        <v>1</v>
+      </c>
+      <c r="P35" s="8">
+        <f>B35*O35</f>
+        <v>5</v>
+      </c>
+      <c r="Q35" s="7">
+        <v>1</v>
+      </c>
+      <c r="R35" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="K23" s="8">
-        <v>2</v>
-      </c>
-      <c r="L23" s="9">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="2">
         <v>35</v>
       </c>
-      <c r="C24" s="8">
-        <v>0</v>
-      </c>
-      <c r="D24" s="8">
+      <c r="C36" s="11">
+        <v>0</v>
+      </c>
+      <c r="D36" s="8">
+        <f t="shared" ref="D36:D38" si="12">B36*C36</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="11">
+        <v>0</v>
+      </c>
+      <c r="F36" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E24" s="8">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="8">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8">
+      <c r="G36" s="11">
+        <v>0</v>
+      </c>
+      <c r="H36" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="11">
+        <v>0</v>
+      </c>
+      <c r="J36" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I24" s="8">
-        <v>0</v>
-      </c>
-      <c r="J24" s="9">
+      <c r="K36" s="7">
+        <v>0</v>
+      </c>
+      <c r="L36" s="8">
+        <f>B36*K36</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="7">
+        <v>0</v>
+      </c>
+      <c r="N36" s="8">
+        <f>B36*M36</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="7">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8">
+        <f>B36*O36</f>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="7">
+        <v>0</v>
+      </c>
+      <c r="R36" s="8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="2">
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="2">
         <v>9</v>
       </c>
-      <c r="C25" s="8">
-        <v>0</v>
-      </c>
-      <c r="D25" s="8">
+      <c r="C37" s="11">
+        <v>0</v>
+      </c>
+      <c r="D37" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E37" s="11">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E25" s="8">
-        <v>0</v>
-      </c>
-      <c r="F25" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="8">
-        <v>0</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="8">
-        <v>0</v>
-      </c>
-      <c r="J25" s="9">
+      <c r="G37" s="11">
+        <v>0</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="11">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8">
+        <f t="shared" ref="J37:J38" si="13">B37*I37</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="7">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8">
+        <f>B37*K37</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="7">
+        <v>0</v>
+      </c>
+      <c r="N37" s="8">
+        <f>B37*M37</f>
+        <v>0</v>
+      </c>
+      <c r="O37" s="7">
+        <v>0</v>
+      </c>
+      <c r="P37" s="8">
+        <f>B37*O37</f>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="7">
+        <v>0</v>
+      </c>
+      <c r="R37" s="8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K25" s="8">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="2">
+    </row>
+    <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="2">
         <v>25</v>
       </c>
-      <c r="C26" s="8">
-        <v>0</v>
-      </c>
-      <c r="D26" s="8">
+      <c r="C38" s="12">
+        <v>0</v>
+      </c>
+      <c r="D38" s="13">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E38" s="12">
+        <v>1</v>
+      </c>
+      <c r="F38" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1</v>
-      </c>
-      <c r="F26" s="8">
-        <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="G26" s="8">
-        <v>1</v>
-      </c>
-      <c r="H26" s="8">
-        <f t="shared" si="3"/>
+      <c r="G38" s="12">
+        <v>1</v>
+      </c>
+      <c r="H38" s="13">
+        <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="I26" s="8">
-        <v>1</v>
-      </c>
-      <c r="J26" s="9">
+      <c r="I38" s="12">
+        <v>1</v>
+      </c>
+      <c r="J38" s="13">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="K38" s="7">
+        <v>0</v>
+      </c>
+      <c r="L38" s="8">
+        <f>B38*K38</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="7">
+        <v>0</v>
+      </c>
+      <c r="N38" s="8">
+        <f>B38*M38</f>
+        <v>0</v>
+      </c>
+      <c r="O38" s="7">
+        <v>0</v>
+      </c>
+      <c r="P38" s="8">
+        <f>B38*O38</f>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>0</v>
+      </c>
+      <c r="R38" s="8">
         <f t="shared" si="4"/>
-        <v>25</v>
-      </c>
-      <c r="K26" s="8">
-        <v>1</v>
-      </c>
-      <c r="L26" s="9">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="10">
-        <f>SUM(D2:D26)</f>
-        <v>188.25</v>
-      </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10">
-        <f>SUM(F2:F26)</f>
-        <v>899.25</v>
-      </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10">
-        <f>SUM(H2:H26)</f>
-        <v>1005.25</v>
-      </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10">
-        <f>SUM(J2:J26)</f>
-        <v>1111.25</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="11">
-        <f>SUM(L2:L26)</f>
-        <v>1251.25</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6">
+        <f>((C7*1500)+(C8*2625))/1000</f>
+        <v>1.5</v>
+      </c>
+      <c r="D39" s="9">
+        <f>SUM(D2:D38)</f>
+        <v>188</v>
+      </c>
+      <c r="E39" s="6">
+        <f>((E7*1500)+(E8*2625))/1000</f>
+        <v>4.125</v>
+      </c>
+      <c r="F39" s="9">
+        <f>SUM(F2:F38)</f>
+        <v>899</v>
+      </c>
+      <c r="G39" s="6">
+        <f>((G7*1500)+(G8*2625))/1000</f>
+        <v>6.75</v>
+      </c>
+      <c r="H39" s="9">
+        <f>SUM(H2:H38)</f>
+        <v>1005</v>
+      </c>
+      <c r="I39" s="6">
+        <f>((I7*1500)+(I8*2625))/1000</f>
+        <v>9.375</v>
+      </c>
+      <c r="J39" s="9">
+        <f>SUM(J2:J38)</f>
+        <v>1111</v>
+      </c>
+      <c r="K39" s="6">
+        <f>((K7*1500)+(K8*2625))/1000</f>
+        <v>12</v>
+      </c>
+      <c r="L39" s="10">
+        <f>SUM(L2:L38)</f>
+        <v>612</v>
+      </c>
+      <c r="M39" s="6">
+        <f>((M7*1500)+(M8*2625))/1000</f>
+        <v>12</v>
+      </c>
+      <c r="N39" s="10">
+        <f>SUM(N2:N38)</f>
+        <v>1019</v>
+      </c>
+      <c r="O39" s="6">
+        <f>((O7*1500)+(O8*2625))/1000</f>
+        <v>12</v>
+      </c>
+      <c r="P39" s="10">
+        <f>SUM(P2:P38)</f>
+        <v>825</v>
+      </c>
+      <c r="Q39" s="6">
+        <f>((Q7*1500)+(Q8*2625))/1000</f>
+        <v>12</v>
+      </c>
+      <c r="R39" s="10">
+        <f>SUM(R2:R38)</f>
+        <v>899</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R40" s="14"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B20 B22:B26">
-    <cfRule type="colorScale" priority="35">
+  <conditionalFormatting sqref="B2:B38">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2111,7 +3560,223 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
+  <conditionalFormatting sqref="B33">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:B38 B2:B32">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D38">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F38">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H38">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J38">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L38">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L33">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N38">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N33">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P38">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2122,9 +3787,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D20 D22:D26">
-    <cfRule type="colorScale" priority="37">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2135,8 +3798,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D21">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="P33">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2147,8 +3810,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F20 F22:F26">
-    <cfRule type="colorScale" priority="39">
+  <conditionalFormatting sqref="R2:R38 R40">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2158,8 +3821,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2171,19 +3842,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H20 H22:H26">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
+  <conditionalFormatting sqref="R33">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2195,44 +3854,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J20 J22:J26">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J21">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20 L22:L26">
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L21">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="B2:B38 D2:D38 F2:F38 H2:H38 J2:J38">
+    <cfRule type="colorScale" priority="63">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2265,551 +3888,551 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
         <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
         <v>89</v>
-      </c>
-      <c r="D19" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" t="s">
         <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="E32" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2836,111 +4459,111 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
